--- a/Project3_ClassSchedule/Class Time -Group Number – Gantt project 3 planner.xlsx
+++ b/Project3_ClassSchedule/Class Time -Group Number – Gantt project 3 planner.xlsx
@@ -5,10 +5,10 @@
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shiek\Documents\ClassSchedule\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shiek\Documents\CSCI331_Group5\Project3_ClassSchedule\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FAFF38-2FF9-4244-91E2-5D813B293869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A58DCD-2C60-4208-A8F8-3B3DC3C60ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -551,6 +551,15 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="11">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="8" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -560,6 +569,12 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="12">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="9" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="9" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="10">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -583,21 +598,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="8" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="9" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="9" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="19">
@@ -621,7 +621,7 @@
     <cellStyle name="Project Headers" xfId="4" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
     <cellStyle name="Title" xfId="8" builtinId="15" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="9">
     <dxf>
       <fill>
         <patternFill>
@@ -751,15 +751,6 @@
         <bottom style="thin">
           <color theme="7"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color theme="7"/>
-        </top>
         <vertical/>
         <horizontal/>
       </border>
@@ -1012,14 +1003,14 @@
   <sheetFormatPr defaultColWidth="2.77734375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" style="29" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" style="18" customWidth="1"/>
     <col min="3" max="6" width="11.6640625" style="1" customWidth="1"/>
     <col min="7" max="7" width="15.6640625" style="3" customWidth="1"/>
     <col min="8" max="27" width="2.77734375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:67" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="1.05">
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="20" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="10"/>
@@ -1029,13 +1020,13 @@
       <c r="G1" s="10"/>
     </row>
     <row r="2" spans="2:67" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
       <c r="G2" s="4" t="s">
         <v>6</v>
       </c>
@@ -1043,66 +1034,66 @@
         <v>1</v>
       </c>
       <c r="J2" s="12"/>
-      <c r="K2" s="24" t="s">
+      <c r="K2" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="26"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="31"/>
       <c r="P2" s="13"/>
-      <c r="Q2" s="24" t="s">
+      <c r="Q2" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27"/>
-      <c r="T2" s="26"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="31"/>
       <c r="U2" s="14"/>
-      <c r="V2" s="18" t="s">
+      <c r="V2" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="W2" s="19"/>
-      <c r="X2" s="19"/>
-      <c r="Y2" s="28"/>
+      <c r="W2" s="22"/>
+      <c r="X2" s="22"/>
+      <c r="Y2" s="33"/>
       <c r="Z2" s="15"/>
-      <c r="AA2" s="18" t="s">
+      <c r="AA2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="AB2" s="19"/>
-      <c r="AC2" s="19"/>
-      <c r="AD2" s="19"/>
-      <c r="AE2" s="19"/>
-      <c r="AF2" s="19"/>
-      <c r="AG2" s="28"/>
+      <c r="AB2" s="22"/>
+      <c r="AC2" s="22"/>
+      <c r="AD2" s="22"/>
+      <c r="AE2" s="22"/>
+      <c r="AF2" s="22"/>
+      <c r="AG2" s="33"/>
       <c r="AH2" s="16"/>
-      <c r="AI2" s="18" t="s">
+      <c r="AI2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="AJ2" s="19"/>
-      <c r="AK2" s="19"/>
-      <c r="AL2" s="19"/>
-      <c r="AM2" s="19"/>
-      <c r="AN2" s="19"/>
-      <c r="AO2" s="19"/>
-      <c r="AP2" s="19"/>
+      <c r="AJ2" s="22"/>
+      <c r="AK2" s="22"/>
+      <c r="AL2" s="22"/>
+      <c r="AM2" s="22"/>
+      <c r="AN2" s="22"/>
+      <c r="AO2" s="22"/>
+      <c r="AP2" s="22"/>
     </row>
     <row r="3" spans="2:67" s="9" customFormat="1" ht="39.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="G3" s="28" t="s">
         <v>11</v>
       </c>
       <c r="H3" s="17" t="s">
@@ -1129,12 +1120,12 @@
       <c r="AA3" s="8"/>
     </row>
     <row r="4" spans="2:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="33"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
       <c r="H4" s="2">
         <v>1</v>
       </c>
@@ -1317,7 +1308,7 @@
       </c>
     </row>
     <row r="5" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="19" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="5">
@@ -1333,11 +1324,11 @@
         <v>2</v>
       </c>
       <c r="G5" s="6">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="19" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="5">
@@ -1357,7 +1348,7 @@
       </c>
     </row>
     <row r="7" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="19" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="5">
@@ -1373,11 +1364,11 @@
         <v>5</v>
       </c>
       <c r="G7" s="6">
-        <v>0.35</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="19" t="s">
         <v>18</v>
       </c>
       <c r="C8" s="5">
@@ -1393,11 +1384,11 @@
         <v>3</v>
       </c>
       <c r="G8" s="6">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:67" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="19" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="5">
@@ -1413,11 +1404,11 @@
         <v>5</v>
       </c>
       <c r="G9" s="6">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:67" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="19" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="5">
@@ -1433,11 +1424,11 @@
         <v>5</v>
       </c>
       <c r="G10" s="6">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="19" t="s">
         <v>21</v>
       </c>
       <c r="C11" s="5">
@@ -1453,11 +1444,11 @@
         <v>4</v>
       </c>
       <c r="G11" s="6">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="19" t="s">
         <v>22</v>
       </c>
       <c r="C12" s="5">
@@ -1473,11 +1464,11 @@
         <v>1</v>
       </c>
       <c r="G12" s="6">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C13" s="5">
@@ -1493,7 +1484,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="6">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1542,7 +1533,7 @@
       <formula>MOD(COLUMN(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="16">
+  <dataValidations disablePrompts="1" count="16">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Project planner uses periods for intervals. Start=1 is period 1 and duration=5 means project spans 5 periods starting from start period. Enter data starting in B5 to update the chart" sqref="A1" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Type a value from 1 to 60 or select a period from the list-press  CANCEL, ALT+DOWN ARROW, then ENTER to select a value" prompt="Enter a period in the range of 1 to 60 or select a period from the list. Press ALT+DOWN ARROW to navigate the list, then ENTER to select a value" sqref="H2" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36,37,38,39,40,41,42,43,44,45,46,47,48,49,50,51,52,53,54,55,56,57,58,59,60"</formula1>
